--- a/data/checklists/nba/1990-91-Hoops-Basketball.xlsx
+++ b/data/checklists/nba/1990-91-Hoops-Basketball.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D420"/>
+  <dimension ref="A1:D514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7936,6 +7936,1586 @@
       </c>
       <c r="D420" t="inlineStr"/>
     </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>David Robinson / Vlade Divac / Tim Hardaway / Pooh Richardson / Sherman Douglas ART, VAR VAR: No stats on back</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>David Robinson / Vlade Divac / Tim Hardaway / Pooh Richardson / Sherman Douglas ART, VAR VAR: Stats on back</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>All-Rookie Team</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Michael Jordan / James Worthy / Isiah Thomas / A.C. Green / Reggie Miller / Akeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>All-Star Program Panels</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Karl Malone / Magic Johnson / Patrick Ewing / David Robinson / Michael Jordan / Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>All-Star Program Panels</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Kevin McHale / Fat Lever / Joe Dumars / Rolando Blackman / Robert Parish / Kevin Johnson</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>All-Star Program Panels</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins / David Robinson / Dennis Rodman / Chris Mullin / Scottie Pippen / Tom Chambers</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>All-Star Program Panels</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Patrick Ewing / Magic Johnson / Larry Bird / John Stockton / Charles Barkley / Clyde Drexler</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>All-Star Program Panels</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Larry Bird</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Rolando Blackman</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Tom Chambers</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Clyde Drexler</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Joe Dumars</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>A.C. Green</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Kevin Johnson</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Magic Johnson</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Lafayette Lever</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Karl Malone</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Kevin McHale</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Reggie Miller</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Chris Mullin</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Akeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Robert Parish</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Scottie Pippen</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>David Robinson</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Dennis Rodman</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>John Stockton</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>James Worthy</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>All-Star Program Perforated</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Marv Albert</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Steve Albert</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Announcers - TV Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>John K. Andariese</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Announcers - Analyst</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Jerry Wayne Baker</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Announcers - TV Broadcaster</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>James Franklin Barnett</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Jim Barniak</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Announcers - Sports Director</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Rick Barry</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Ron Boone</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Mark J. Boyle</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Hubie Brown</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Kevin Paul Calabro</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Harry Christopher Caray III</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Skip Caray</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Doug Collins</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Chet William Coppock</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Announcers - UER Studio Host;</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Bob Costas</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Announcers - Studio Co-Host</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>James A. Durham</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Dick Enberg</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Don Fish</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Announcers - SPON Senior VP Sales &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>James Anthony Foley</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Announcers - Director of Communications</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Michael Robert Fratello</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Gary L. Gerould</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Announcers - Radio Voice</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Jack Givens</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Michael Thomas Gorman</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Thomas Donn Hanneman</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Announcers - Broadcast Anchor</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Kevin Robert Harlan</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Dick Harter</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Announcers - Analyst</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Fred Hickman</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Announcers - Co-host "Inside the NBA"</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Steven R. Holman</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Announcers - Sports Director / Radio Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Jay Howard</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Announcers - Sports Director</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>James R. Irwin</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play Announcer</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Daniel Paul Issel</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Announcers - Analyst</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Ernie Johnson Jr.</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Announcers - Studio Host</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Stephen H. Jones</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>John "Red" Kerr</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Jeffrey Brooks Kingery</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Ralph Lawler</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Announcers - Announcer</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Joseph Fredrick McConnell</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play Announcer</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>L. Allen McCoy</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Announcers - Vice President - Broadcasting</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Jonathan Miller</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Announcers - Vice President - Programming</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Bob Neal</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Glenn Ordway</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Melbourne John Proctor</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Announcers - TV Play-by-Play Announcer</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Edwin Wayne Randall</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Announcers - Broadcaster</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Mike Rice</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Announcers - Color Analyst</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Pat Riley</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Announcers - Studio Co-Host</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Andrew Rosenberg</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Announcers - Director</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Tommy Roy</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Announcers - Coordinating Producer NBA</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Tim James Roye</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Announcers - Host Sports Director PBP</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Craig Sager</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Announcers - Studio Host</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Bill Schonely</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Charles Martin Slowes</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Announcers - Radio Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>David Preston Steele</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Announcers - Radio Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Hannah Storm</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Announcers - Co-host "Inside the NBA"</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Ron Thulin</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Gerry E. Vaillancourt</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Announcers - Sports Director / Color Analyst</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Pete Van Wieren</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Announcers - Play-by-Play</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>William H. Worrell Jr.</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Announcers - Sports Director</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>John Bagley</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>James Donaldson</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Ron Harper</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Sedale Threatt</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
